--- a/WorkBot/refactor/data/orders/UNFI/UNFI_Bakery_2025-10-11.xlsx
+++ b/WorkBot/refactor/data/orders/UNFI/UNFI_Bakery_2025-10-11.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1091,6 +1091,60 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>183096-7</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Clio - Greek Yogurt Bar Strawberry</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>16.65</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>33.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>183090-0</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Clio - Greek Yogurt Bar Vanilla</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>16.65</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>33.30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
